--- a/artfynd/A 70039-2021 artfynd.xlsx
+++ b/artfynd/A 70039-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 70039-2021 artfynd.xlsx
+++ b/artfynd/A 70039-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,113 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129202405</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101927</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Knutsberg V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>602196</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6555866</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägslänt skogsväg</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 70039-2021 artfynd.xlsx
+++ b/artfynd/A 70039-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,6 +905,113 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129219776</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100847</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Knutsberg V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>602196</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6555866</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 70039-2021 artfynd.xlsx
+++ b/artfynd/A 70039-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129202405</v>
       </c>
       <c r="B3" t="n">
-        <v>101927</v>
+        <v>101937</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129219776</v>
       </c>
       <c r="B4" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 70039-2021 artfynd.xlsx
+++ b/artfynd/A 70039-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129202405</v>
       </c>
       <c r="B3" t="n">
-        <v>101937</v>
+        <v>101944</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129219776</v>
       </c>
       <c r="B4" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 70039-2021 artfynd.xlsx
+++ b/artfynd/A 70039-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129202405</v>
       </c>
       <c r="B3" t="n">
-        <v>101944</v>
+        <v>101946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129219776</v>
       </c>
       <c r="B4" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 70039-2021 artfynd.xlsx
+++ b/artfynd/A 70039-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129202405</v>
       </c>
       <c r="B3" t="n">
-        <v>101946</v>
+        <v>101972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129219776</v>
       </c>
       <c r="B4" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 70039-2021 artfynd.xlsx
+++ b/artfynd/A 70039-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129202405</v>
       </c>
       <c r="B3" t="n">
-        <v>101972</v>
+        <v>101974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129219776</v>
       </c>
       <c r="B4" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 70039-2021 artfynd.xlsx
+++ b/artfynd/A 70039-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129202405</v>
       </c>
       <c r="B3" t="n">
-        <v>101974</v>
+        <v>101975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129219776</v>
       </c>
       <c r="B4" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 70039-2021 artfynd.xlsx
+++ b/artfynd/A 70039-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129202405</v>
       </c>
       <c r="B3" t="n">
-        <v>101975</v>
+        <v>101979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129219776</v>
       </c>
       <c r="B4" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 70039-2021 artfynd.xlsx
+++ b/artfynd/A 70039-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129202405</v>
       </c>
       <c r="B3" t="n">
-        <v>101979</v>
+        <v>101981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129219776</v>
       </c>
       <c r="B4" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 70039-2021 artfynd.xlsx
+++ b/artfynd/A 70039-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129202405</v>
       </c>
       <c r="B3" t="n">
-        <v>101981</v>
+        <v>101985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129219776</v>
       </c>
       <c r="B4" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 70039-2021 artfynd.xlsx
+++ b/artfynd/A 70039-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129202405</v>
       </c>
       <c r="B3" t="n">
-        <v>101985</v>
+        <v>101995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129219776</v>
       </c>
       <c r="B4" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 70039-2021 artfynd.xlsx
+++ b/artfynd/A 70039-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129202405</v>
       </c>
       <c r="B3" t="n">
-        <v>101995</v>
+        <v>101998</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129219776</v>
       </c>
       <c r="B4" t="n">
-        <v>100913</v>
+        <v>100916</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 70039-2021 artfynd.xlsx
+++ b/artfynd/A 70039-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129202405</v>
       </c>
       <c r="B3" t="n">
-        <v>101998</v>
+        <v>102027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129219776</v>
       </c>
       <c r="B4" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 70039-2021 artfynd.xlsx
+++ b/artfynd/A 70039-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>111774774</v>
       </c>
       <c r="B2" t="n">
-        <v>101267</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129202405</v>
+        <v>96480034</v>
       </c>
       <c r="B3" t="n">
-        <v>102027</v>
+        <v>109815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221317</v>
+        <v>220204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,17 +830,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knutsberg V om, Srm</t>
+          <t>Knutsberg 100m v, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602196</v>
+        <v>602371</v>
       </c>
       <c r="R3" t="n">
-        <v>6555866</v>
+        <v>6555922</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,12 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Vägslänt skogsväg</t>
+          <t>Skogsbryn</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -907,32 +902,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129219776</v>
+        <v>96479983</v>
       </c>
       <c r="B4" t="n">
-        <v>100945</v>
+        <v>110078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,17 +937,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knutsberg V om, Srm</t>
+          <t>Knutsberg 400m v, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602196</v>
+        <v>602149</v>
       </c>
       <c r="R4" t="n">
-        <v>6555866</v>
+        <v>6555840</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +991,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Frisk gräsmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1011,6 +1006,220 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129202405</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102418</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Knutsberg V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>602196</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6555866</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vägslänt skogsväg</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129219776</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Knutsberg V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>602196</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6555866</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 70039-2021 artfynd.xlsx
+++ b/artfynd/A 70039-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111774774</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96480034</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96479983</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129202405</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1220,8 +1245,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129219776</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>